--- a/VtigerCrm/src/test/resources/TestData/Book2.xlsx
+++ b/VtigerCrm/src/test/resources/TestData/Book2.xlsx
@@ -33,7 +33,7 @@
     <t>lastname</t>
   </si>
   <si>
-    <t>Ranjan</t>
+    <t>Singh</t>
   </si>
 </sst>
 </file>
